--- a/data/raw/GLNPO 2024 Spring/Huron/D20/Zoops/HU 61 D20 QA Spring 2024 24GH02Q74 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Huron/D20/Zoops/HU 61 D20 QA Spring 2024 24GH02Q74 Zoop.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Huron\D20\Zoops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65837FC0-F99E-4888-AB8B-A5F68974C968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F3385D-0054-4D7C-B68E-F5D23935E86B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6D1FDE3E-6719-49BA-9F61-2AC28C8DE547}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6D1FDE3E-6719-49BA-9F61-2AC28C8DE547}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Y$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$151</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId2"/>
+    <pivotCache cacheId="20" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="71">
   <si>
     <t>SAMPLENUM</t>
   </si>
@@ -224,9 +224,6 @@
     <t>Column Labels</t>
   </si>
   <si>
-    <t>CALIM</t>
-  </si>
-  <si>
     <t>Calibration Table:</t>
   </si>
   <si>
@@ -319,7 +316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -329,7 +326,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3285,7 +3281,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B136E1C2-44DE-459E-8694-7E4BB02EA264}" name="PivotTable3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B136E1C2-44DE-459E-8694-7E4BB02EA264}" name="PivotTable3" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T3:X15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -3716,24 +3712,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5124763D-8627-4458-AC86-27EBBD8020BE}">
   <dimension ref="A1:X151"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="11" max="11" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="2.44140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="22" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3789,7 +3785,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3818,7 +3814,7 @@
         <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K2" t="s">
         <v>25</v>
@@ -3842,7 +3838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3871,7 +3867,7 @@
         <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K3" t="s">
         <v>30</v>
@@ -3901,7 +3897,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -3930,7 +3926,7 @@
         <v>24</v>
       </c>
       <c r="J4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K4" t="s">
         <v>25</v>
@@ -3969,7 +3965,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -3998,7 +3994,7 @@
         <v>24</v>
       </c>
       <c r="J5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K5" t="s">
         <v>35</v>
@@ -4024,18 +4020,17 @@
       <c r="T5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="U5" s="7">
+      <c r="U5">
         <v>13</v>
       </c>
-      <c r="V5" s="7">
+      <c r="V5">
         <v>25</v>
       </c>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7">
+      <c r="X5">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -4064,7 +4059,7 @@
         <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K6" t="s">
         <v>38</v>
@@ -4090,18 +4085,17 @@
       <c r="T6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="U6" s="7">
+      <c r="U6">
         <v>7</v>
       </c>
-      <c r="V6" s="7">
-        <v>18</v>
-      </c>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7">
+      <c r="V6">
+        <v>18</v>
+      </c>
+      <c r="X6">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -4130,7 +4124,7 @@
         <v>24</v>
       </c>
       <c r="J7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K7" t="s">
         <v>25</v>
@@ -4156,18 +4150,17 @@
       <c r="T7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="U7" s="7">
+      <c r="U7">
         <v>17</v>
       </c>
-      <c r="V7" s="7">
-        <v>32</v>
-      </c>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7">
+      <c r="V7">
+        <v>32</v>
+      </c>
+      <c r="X7">
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -4196,7 +4189,7 @@
         <v>24</v>
       </c>
       <c r="J8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K8" t="s">
         <v>35</v>
@@ -4222,16 +4215,14 @@
       <c r="T8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="U8" s="7">
+      <c r="U8">
         <v>42</v>
       </c>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7">
+      <c r="X8">
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -4260,7 +4251,7 @@
         <v>24</v>
       </c>
       <c r="J9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K9" t="s">
         <v>42</v>
@@ -4286,16 +4277,14 @@
       <c r="T9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="U9" s="7">
+      <c r="U9">
         <v>41</v>
       </c>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7">
+      <c r="X9">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -4324,7 +4313,7 @@
         <v>24</v>
       </c>
       <c r="J10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K10" t="s">
         <v>44</v>
@@ -4350,16 +4339,14 @@
       <c r="T10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="U10" s="7">
+      <c r="U10">
         <v>39</v>
       </c>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7">
+      <c r="X10">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -4388,7 +4375,7 @@
         <v>24</v>
       </c>
       <c r="J11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K11" t="s">
         <v>35</v>
@@ -4414,20 +4401,20 @@
       <c r="T11" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="U11" s="7">
-        <v>1</v>
-      </c>
-      <c r="V11" s="7">
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
         <v>0</v>
       </c>
-      <c r="W11" s="7">
+      <c r="W11">
         <v>3</v>
       </c>
-      <c r="X11" s="7">
+      <c r="X11">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -4456,7 +4443,7 @@
         <v>24</v>
       </c>
       <c r="J12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K12" t="s">
         <v>30</v>
@@ -4482,20 +4469,20 @@
       <c r="T12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="U12" s="7">
-        <v>1</v>
-      </c>
-      <c r="V12" s="7">
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
         <v>0</v>
       </c>
-      <c r="W12" s="7">
+      <c r="W12">
         <v>0</v>
       </c>
-      <c r="X12" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -4524,7 +4511,7 @@
         <v>24</v>
       </c>
       <c r="J13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K13" t="s">
         <v>46</v>
@@ -4550,18 +4537,17 @@
       <c r="T13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="U13" s="7">
-        <v>1</v>
-      </c>
-      <c r="V13" s="7">
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
         <v>0</v>
       </c>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -4590,7 +4576,7 @@
         <v>24</v>
       </c>
       <c r="J14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K14" t="s">
         <v>35</v>
@@ -4616,18 +4602,17 @@
       <c r="T14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="U14" s="7">
+      <c r="U14">
         <v>3</v>
       </c>
-      <c r="V14" s="7">
+      <c r="V14">
         <v>0</v>
       </c>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7">
+      <c r="X14">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -4656,7 +4641,7 @@
         <v>24</v>
       </c>
       <c r="J15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K15" t="s">
         <v>42</v>
@@ -4682,20 +4667,20 @@
       <c r="T15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="U15" s="7">
+      <c r="U15">
         <v>165</v>
       </c>
-      <c r="V15" s="7">
+      <c r="V15">
         <v>75</v>
       </c>
-      <c r="W15" s="7">
+      <c r="W15">
         <v>3</v>
       </c>
-      <c r="X15" s="7">
+      <c r="X15">
         <v>243</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -4724,7 +4709,7 @@
         <v>24</v>
       </c>
       <c r="J16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K16" t="s">
         <v>46</v>
@@ -4748,7 +4733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -4777,7 +4762,7 @@
         <v>24</v>
       </c>
       <c r="J17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K17" t="s">
         <v>46</v>
@@ -4801,7 +4786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -4830,7 +4815,7 @@
         <v>24</v>
       </c>
       <c r="J18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K18" t="s">
         <v>46</v>
@@ -4854,7 +4839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -4883,7 +4868,7 @@
         <v>24</v>
       </c>
       <c r="J19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K19" t="s">
         <v>46</v>
@@ -4907,12 +4892,12 @@
         <v>1</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="U19" s="5"/>
       <c r="V19" s="5"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -4941,7 +4926,7 @@
         <v>24</v>
       </c>
       <c r="J20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K20" t="s">
         <v>46</v>
@@ -4965,16 +4950,16 @@
         <v>1</v>
       </c>
       <c r="T20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="U20" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="U20" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="V20" s="6">
         <v>1.004</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -5003,7 +4988,7 @@
         <v>24</v>
       </c>
       <c r="J21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K21" t="s">
         <v>46</v>
@@ -5028,13 +5013,13 @@
       </c>
       <c r="T21" s="4"/>
       <c r="U21" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V21" s="6">
         <v>1.002</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -5063,7 +5048,7 @@
         <v>24</v>
       </c>
       <c r="J22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K22" t="s">
         <v>42</v>
@@ -5087,16 +5072,16 @@
         <v>1</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U22" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V22" s="6">
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -5125,7 +5110,7 @@
         <v>24</v>
       </c>
       <c r="J23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K23" t="s">
         <v>42</v>
@@ -5150,13 +5135,13 @@
       </c>
       <c r="T23" s="4"/>
       <c r="U23" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V23" s="5">
         <v>0.998</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -5185,7 +5170,7 @@
         <v>24</v>
       </c>
       <c r="J24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K24" t="s">
         <v>42</v>
@@ -5209,14 +5194,14 @@
         <v>1</v>
       </c>
       <c r="T24" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="U24" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="U24" s="5" t="s">
-        <v>66</v>
-      </c>
       <c r="V24" s="5"/>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -5245,7 +5230,7 @@
         <v>24</v>
       </c>
       <c r="J25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K25" t="s">
         <v>30</v>
@@ -5269,14 +5254,14 @@
         <v>1</v>
       </c>
       <c r="T25" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="U25" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="U25" s="5" t="s">
-        <v>68</v>
-      </c>
       <c r="V25" s="5"/>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -5305,7 +5290,7 @@
         <v>24</v>
       </c>
       <c r="J26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K26" t="s">
         <v>42</v>
@@ -5329,14 +5314,14 @@
         <v>1</v>
       </c>
       <c r="T26" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U26" s="5"/>
       <c r="V26" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -5365,7 +5350,7 @@
         <v>24</v>
       </c>
       <c r="J27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K27" t="s">
         <v>25</v>
@@ -5389,7 +5374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -5418,7 +5403,7 @@
         <v>24</v>
       </c>
       <c r="J28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K28" t="s">
         <v>25</v>
@@ -5442,7 +5427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -5471,7 +5456,7 @@
         <v>24</v>
       </c>
       <c r="J29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K29" t="s">
         <v>30</v>
@@ -5495,7 +5480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -5524,7 +5509,7 @@
         <v>24</v>
       </c>
       <c r="J30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K30" t="s">
         <v>38</v>
@@ -5548,7 +5533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -5577,7 +5562,7 @@
         <v>24</v>
       </c>
       <c r="J31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K31" t="s">
         <v>46</v>
@@ -5601,7 +5586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -5630,7 +5615,7 @@
         <v>24</v>
       </c>
       <c r="J32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K32" t="s">
         <v>38</v>
@@ -5654,7 +5639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -5683,7 +5668,7 @@
         <v>24</v>
       </c>
       <c r="J33" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K33" t="s">
         <v>25</v>
@@ -5707,7 +5692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -5736,7 +5721,7 @@
         <v>24</v>
       </c>
       <c r="J34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K34" t="s">
         <v>25</v>
@@ -5760,7 +5745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -5789,7 +5774,7 @@
         <v>24</v>
       </c>
       <c r="J35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K35" t="s">
         <v>44</v>
@@ -5813,7 +5798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -5842,7 +5827,7 @@
         <v>24</v>
       </c>
       <c r="J36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K36" t="s">
         <v>25</v>
@@ -5866,7 +5851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -5895,7 +5880,7 @@
         <v>24</v>
       </c>
       <c r="J37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K37" t="s">
         <v>30</v>
@@ -5919,7 +5904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -5948,7 +5933,7 @@
         <v>24</v>
       </c>
       <c r="J38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K38" t="s">
         <v>46</v>
@@ -5972,7 +5957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -6001,7 +5986,7 @@
         <v>24</v>
       </c>
       <c r="J39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K39" t="s">
         <v>30</v>
@@ -6025,7 +6010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -6054,7 +6039,7 @@
         <v>24</v>
       </c>
       <c r="J40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K40" t="s">
         <v>30</v>
@@ -6078,7 +6063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -6107,7 +6092,7 @@
         <v>24</v>
       </c>
       <c r="J41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K41" t="s">
         <v>42</v>
@@ -6131,7 +6116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -6160,7 +6145,7 @@
         <v>24</v>
       </c>
       <c r="J42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K42" t="s">
         <v>42</v>
@@ -6184,7 +6169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -6213,7 +6198,7 @@
         <v>24</v>
       </c>
       <c r="J43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K43" t="s">
         <v>42</v>
@@ -6237,7 +6222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -6266,7 +6251,7 @@
         <v>24</v>
       </c>
       <c r="J44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K44" t="s">
         <v>48</v>
@@ -6290,7 +6275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -6319,7 +6304,7 @@
         <v>24</v>
       </c>
       <c r="J45" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K45" t="s">
         <v>50</v>
@@ -6343,7 +6328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -6372,7 +6357,7 @@
         <v>24</v>
       </c>
       <c r="J46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K46" t="s">
         <v>46</v>
@@ -6396,7 +6381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -6425,7 +6410,7 @@
         <v>24</v>
       </c>
       <c r="J47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K47" t="s">
         <v>25</v>
@@ -6449,7 +6434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -6478,7 +6463,7 @@
         <v>24</v>
       </c>
       <c r="J48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K48" t="s">
         <v>46</v>
@@ -6502,7 +6487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -6531,7 +6516,7 @@
         <v>24</v>
       </c>
       <c r="J49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K49" t="s">
         <v>38</v>
@@ -6555,7 +6540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -6584,7 +6569,7 @@
         <v>24</v>
       </c>
       <c r="J50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K50" t="s">
         <v>42</v>
@@ -6608,7 +6593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -6637,7 +6622,7 @@
         <v>24</v>
       </c>
       <c r="J51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K51" t="s">
         <v>38</v>
@@ -6661,7 +6646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -6690,7 +6675,7 @@
         <v>24</v>
       </c>
       <c r="J52" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K52" t="s">
         <v>46</v>
@@ -6714,7 +6699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -6743,7 +6728,7 @@
         <v>24</v>
       </c>
       <c r="J53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K53" t="s">
         <v>30</v>
@@ -6767,7 +6752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -6796,7 +6781,7 @@
         <v>24</v>
       </c>
       <c r="J54" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K54" t="s">
         <v>42</v>
@@ -6820,7 +6805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -6849,7 +6834,7 @@
         <v>24</v>
       </c>
       <c r="J55" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K55" t="s">
         <v>35</v>
@@ -6873,7 +6858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -6902,7 +6887,7 @@
         <v>24</v>
       </c>
       <c r="J56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K56" t="s">
         <v>25</v>
@@ -6926,7 +6911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -6955,7 +6940,7 @@
         <v>24</v>
       </c>
       <c r="J57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K57" t="s">
         <v>38</v>
@@ -6979,7 +6964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -7008,7 +6993,7 @@
         <v>24</v>
       </c>
       <c r="J58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K58" t="s">
         <v>30</v>
@@ -7032,7 +7017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -7061,7 +7046,7 @@
         <v>24</v>
       </c>
       <c r="J59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K59" t="s">
         <v>42</v>
@@ -7085,7 +7070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -7114,7 +7099,7 @@
         <v>24</v>
       </c>
       <c r="J60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K60" t="s">
         <v>42</v>
@@ -7138,7 +7123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -7167,7 +7152,7 @@
         <v>24</v>
       </c>
       <c r="J61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K61" t="s">
         <v>46</v>
@@ -7191,7 +7176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -7220,7 +7205,7 @@
         <v>24</v>
       </c>
       <c r="J62" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K62" t="s">
         <v>25</v>
@@ -7244,7 +7229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -7273,7 +7258,7 @@
         <v>24</v>
       </c>
       <c r="J63" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K63" t="s">
         <v>46</v>
@@ -7297,7 +7282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -7326,7 +7311,7 @@
         <v>24</v>
       </c>
       <c r="J64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K64" t="s">
         <v>38</v>
@@ -7350,7 +7335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -7379,7 +7364,7 @@
         <v>24</v>
       </c>
       <c r="J65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K65" t="s">
         <v>38</v>
@@ -7403,7 +7388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -7432,7 +7417,7 @@
         <v>24</v>
       </c>
       <c r="J66" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K66" t="s">
         <v>38</v>
@@ -7456,7 +7441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -7485,7 +7470,7 @@
         <v>24</v>
       </c>
       <c r="J67" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K67" t="s">
         <v>30</v>
@@ -7509,7 +7494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -7538,7 +7523,7 @@
         <v>24</v>
       </c>
       <c r="J68" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K68" t="s">
         <v>25</v>
@@ -7562,7 +7547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -7591,7 +7576,7 @@
         <v>24</v>
       </c>
       <c r="J69" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K69" t="s">
         <v>30</v>
@@ -7615,7 +7600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -7644,7 +7629,7 @@
         <v>24</v>
       </c>
       <c r="J70" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K70" t="s">
         <v>46</v>
@@ -7668,7 +7653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -7697,7 +7682,7 @@
         <v>24</v>
       </c>
       <c r="J71" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K71" t="s">
         <v>30</v>
@@ -7721,7 +7706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -7750,7 +7735,7 @@
         <v>24</v>
       </c>
       <c r="J72" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K72" t="s">
         <v>42</v>
@@ -7774,7 +7759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -7803,7 +7788,7 @@
         <v>24</v>
       </c>
       <c r="J73" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K73" t="s">
         <v>30</v>
@@ -7827,7 +7812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -7856,7 +7841,7 @@
         <v>24</v>
       </c>
       <c r="J74" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K74" t="s">
         <v>42</v>
@@ -7880,7 +7865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -7909,7 +7894,7 @@
         <v>24</v>
       </c>
       <c r="J75" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K75" t="s">
         <v>42</v>
@@ -7933,7 +7918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -7962,7 +7947,7 @@
         <v>24</v>
       </c>
       <c r="J76" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K76" t="s">
         <v>52</v>
@@ -7986,7 +7971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -8015,7 +8000,7 @@
         <v>24</v>
       </c>
       <c r="J77" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K77" t="s">
         <v>42</v>
@@ -8039,7 +8024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -8068,7 +8053,7 @@
         <v>24</v>
       </c>
       <c r="J78" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K78" t="s">
         <v>30</v>
@@ -8092,7 +8077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -8121,7 +8106,7 @@
         <v>24</v>
       </c>
       <c r="J79" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K79" t="s">
         <v>46</v>
@@ -8145,7 +8130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -8174,7 +8159,7 @@
         <v>24</v>
       </c>
       <c r="J80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K80" t="s">
         <v>35</v>
@@ -8198,7 +8183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -8227,7 +8212,7 @@
         <v>24</v>
       </c>
       <c r="J81" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K81" t="s">
         <v>25</v>
@@ -8251,7 +8236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -8280,7 +8265,7 @@
         <v>24</v>
       </c>
       <c r="J82" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K82" t="s">
         <v>42</v>
@@ -8304,7 +8289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -8333,7 +8318,7 @@
         <v>24</v>
       </c>
       <c r="J83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K83" t="s">
         <v>30</v>
@@ -8357,7 +8342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -8386,7 +8371,7 @@
         <v>24</v>
       </c>
       <c r="J84" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K84" t="s">
         <v>30</v>
@@ -8410,7 +8395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -8439,7 +8424,7 @@
         <v>24</v>
       </c>
       <c r="J85" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K85" t="s">
         <v>25</v>
@@ -8463,7 +8448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -8492,7 +8477,7 @@
         <v>24</v>
       </c>
       <c r="J86" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K86" t="s">
         <v>25</v>
@@ -8516,7 +8501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -8545,7 +8530,7 @@
         <v>24</v>
       </c>
       <c r="J87" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K87" t="s">
         <v>38</v>
@@ -8569,7 +8554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -8598,7 +8583,7 @@
         <v>24</v>
       </c>
       <c r="J88" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K88" t="s">
         <v>42</v>
@@ -8622,7 +8607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -8651,7 +8636,7 @@
         <v>24</v>
       </c>
       <c r="J89" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K89" t="s">
         <v>46</v>
@@ -8675,7 +8660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -8704,7 +8689,7 @@
         <v>24</v>
       </c>
       <c r="J90" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K90" t="s">
         <v>42</v>
@@ -8728,7 +8713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -8757,7 +8742,7 @@
         <v>24</v>
       </c>
       <c r="J91" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K91" t="s">
         <v>46</v>
@@ -8781,7 +8766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -8810,7 +8795,7 @@
         <v>24</v>
       </c>
       <c r="J92" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K92" t="s">
         <v>38</v>
@@ -8834,7 +8819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -8863,7 +8848,7 @@
         <v>24</v>
       </c>
       <c r="J93" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K93" t="s">
         <v>30</v>
@@ -8887,7 +8872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -8916,7 +8901,7 @@
         <v>24</v>
       </c>
       <c r="J94" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K94" t="s">
         <v>42</v>
@@ -8940,7 +8925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -8969,7 +8954,7 @@
         <v>24</v>
       </c>
       <c r="J95" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K95" t="s">
         <v>46</v>
@@ -8993,7 +8978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -9022,7 +9007,7 @@
         <v>24</v>
       </c>
       <c r="J96" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K96" t="s">
         <v>38</v>
@@ -9046,7 +9031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -9075,7 +9060,7 @@
         <v>24</v>
       </c>
       <c r="J97" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K97" t="s">
         <v>44</v>
@@ -9099,7 +9084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -9128,7 +9113,7 @@
         <v>24</v>
       </c>
       <c r="J98" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K98" t="s">
         <v>42</v>
@@ -9152,7 +9137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -9181,7 +9166,7 @@
         <v>24</v>
       </c>
       <c r="J99" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K99" t="s">
         <v>35</v>
@@ -9205,7 +9190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -9234,7 +9219,7 @@
         <v>24</v>
       </c>
       <c r="J100" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K100" t="s">
         <v>25</v>
@@ -9258,7 +9243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -9287,7 +9272,7 @@
         <v>24</v>
       </c>
       <c r="J101" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K101" t="s">
         <v>38</v>
@@ -9311,7 +9296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -9340,7 +9325,7 @@
         <v>24</v>
       </c>
       <c r="J102" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K102" t="s">
         <v>30</v>
@@ -9364,7 +9349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -9393,7 +9378,7 @@
         <v>24</v>
       </c>
       <c r="J103" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K103" t="s">
         <v>42</v>
@@ -9417,7 +9402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -9446,7 +9431,7 @@
         <v>24</v>
       </c>
       <c r="J104" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K104" t="s">
         <v>46</v>
@@ -9470,7 +9455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -9499,7 +9484,7 @@
         <v>24</v>
       </c>
       <c r="J105" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K105" t="s">
         <v>25</v>
@@ -9523,7 +9508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -9552,7 +9537,7 @@
         <v>24</v>
       </c>
       <c r="J106" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K106" t="s">
         <v>46</v>
@@ -9576,7 +9561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -9605,7 +9590,7 @@
         <v>24</v>
       </c>
       <c r="J107" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K107" t="s">
         <v>30</v>
@@ -9629,7 +9614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -9658,7 +9643,7 @@
         <v>24</v>
       </c>
       <c r="J108" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K108" t="s">
         <v>30</v>
@@ -9682,7 +9667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -9711,7 +9696,7 @@
         <v>24</v>
       </c>
       <c r="J109" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K109" t="s">
         <v>30</v>
@@ -9735,7 +9720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -9764,7 +9749,7 @@
         <v>24</v>
       </c>
       <c r="J110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K110" t="s">
         <v>30</v>
@@ -9788,7 +9773,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -9817,7 +9802,7 @@
         <v>24</v>
       </c>
       <c r="J111" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K111" t="s">
         <v>46</v>
@@ -9841,7 +9826,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -9870,7 +9855,7 @@
         <v>24</v>
       </c>
       <c r="J112" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K112" t="s">
         <v>46</v>
@@ -9894,7 +9879,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -9923,7 +9908,7 @@
         <v>24</v>
       </c>
       <c r="J113" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K113" t="s">
         <v>42</v>
@@ -9947,7 +9932,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -9976,7 +9961,7 @@
         <v>24</v>
       </c>
       <c r="J114" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K114" t="s">
         <v>42</v>
@@ -10000,7 +9985,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -10029,7 +10014,7 @@
         <v>24</v>
       </c>
       <c r="J115" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K115" t="s">
         <v>35</v>
@@ -10053,7 +10038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -10082,7 +10067,7 @@
         <v>24</v>
       </c>
       <c r="J116" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K116" t="s">
         <v>25</v>
@@ -10106,7 +10091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -10135,7 +10120,7 @@
         <v>24</v>
       </c>
       <c r="J117" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K117" t="s">
         <v>38</v>
@@ -10159,7 +10144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -10188,7 +10173,7 @@
         <v>24</v>
       </c>
       <c r="J118" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K118" t="s">
         <v>35</v>
@@ -10212,7 +10197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -10241,7 +10226,7 @@
         <v>24</v>
       </c>
       <c r="J119" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K119" t="s">
         <v>38</v>
@@ -10265,7 +10250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -10294,7 +10279,7 @@
         <v>24</v>
       </c>
       <c r="J120" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K120" t="s">
         <v>35</v>
@@ -10318,7 +10303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -10347,7 +10332,7 @@
         <v>24</v>
       </c>
       <c r="J121" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K121" t="s">
         <v>38</v>
@@ -10371,7 +10356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -10400,7 +10385,7 @@
         <v>24</v>
       </c>
       <c r="J122" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K122" t="s">
         <v>38</v>
@@ -10424,7 +10409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -10453,7 +10438,7 @@
         <v>24</v>
       </c>
       <c r="J123" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K123" t="s">
         <v>35</v>
@@ -10477,7 +10462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -10506,7 +10491,7 @@
         <v>24</v>
       </c>
       <c r="J124" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K124" t="s">
         <v>35</v>
@@ -10530,7 +10515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -10559,7 +10544,7 @@
         <v>24</v>
       </c>
       <c r="J125" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K125" t="s">
         <v>38</v>
@@ -10583,7 +10568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -10612,7 +10597,7 @@
         <v>24</v>
       </c>
       <c r="J126" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K126" t="s">
         <v>35</v>
@@ -10636,7 +10621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -10665,7 +10650,7 @@
         <v>24</v>
       </c>
       <c r="J127" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K127" t="s">
         <v>35</v>
@@ -10689,7 +10674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -10718,7 +10703,7 @@
         <v>24</v>
       </c>
       <c r="J128" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K128" t="s">
         <v>35</v>
@@ -10742,7 +10727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -10771,7 +10756,7 @@
         <v>24</v>
       </c>
       <c r="J129" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K129" t="s">
         <v>38</v>
@@ -10795,7 +10780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -10824,7 +10809,7 @@
         <v>24</v>
       </c>
       <c r="J130" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K130" t="s">
         <v>25</v>
@@ -10848,7 +10833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -10877,7 +10862,7 @@
         <v>24</v>
       </c>
       <c r="J131" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K131" t="s">
         <v>35</v>
@@ -10901,7 +10886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -10930,7 +10915,7 @@
         <v>24</v>
       </c>
       <c r="J132" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K132" t="s">
         <v>38</v>
@@ -10954,7 +10939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -10983,7 +10968,7 @@
         <v>24</v>
       </c>
       <c r="J133" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K133" t="s">
         <v>35</v>
@@ -11007,7 +10992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -11036,7 +11021,7 @@
         <v>24</v>
       </c>
       <c r="J134" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K134" t="s">
         <v>25</v>
@@ -11060,7 +11045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -11089,7 +11074,7 @@
         <v>24</v>
       </c>
       <c r="J135" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K135" t="s">
         <v>35</v>
@@ -11113,7 +11098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -11142,7 +11127,7 @@
         <v>24</v>
       </c>
       <c r="J136" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K136" t="s">
         <v>25</v>
@@ -11166,7 +11151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -11195,7 +11180,7 @@
         <v>24</v>
       </c>
       <c r="J137" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K137" t="s">
         <v>35</v>
@@ -11219,7 +11204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -11248,7 +11233,7 @@
         <v>24</v>
       </c>
       <c r="J138" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K138" t="s">
         <v>35</v>
@@ -11272,7 +11257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -11301,7 +11286,7 @@
         <v>24</v>
       </c>
       <c r="J139" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K139" t="s">
         <v>35</v>
@@ -11325,7 +11310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -11354,7 +11339,7 @@
         <v>24</v>
       </c>
       <c r="J140" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K140" t="s">
         <v>35</v>
@@ -11378,7 +11363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -11407,7 +11392,7 @@
         <v>24</v>
       </c>
       <c r="J141" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K141" t="s">
         <v>35</v>
@@ -11431,7 +11416,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -11460,7 +11445,7 @@
         <v>24</v>
       </c>
       <c r="J142" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K142" t="s">
         <v>25</v>
@@ -11484,7 +11469,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -11513,7 +11498,7 @@
         <v>24</v>
       </c>
       <c r="J143" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K143" t="s">
         <v>38</v>
@@ -11537,7 +11522,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -11566,7 +11551,7 @@
         <v>24</v>
       </c>
       <c r="J144" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K144" t="s">
         <v>52</v>
@@ -11590,7 +11575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -11619,7 +11604,7 @@
         <v>24</v>
       </c>
       <c r="J145" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K145" t="s">
         <v>52</v>
@@ -11643,7 +11628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -11672,7 +11657,7 @@
         <v>24</v>
       </c>
       <c r="J146" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K146" t="s">
         <v>52</v>
@@ -11696,7 +11681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -11725,7 +11710,7 @@
         <v>24</v>
       </c>
       <c r="J147" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K147" t="s">
         <v>52</v>
@@ -11749,7 +11734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -11778,7 +11763,7 @@
         <v>24</v>
       </c>
       <c r="J148" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K148" t="s">
         <v>44</v>
@@ -11802,7 +11787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -11831,7 +11816,7 @@
         <v>24</v>
       </c>
       <c r="J149" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K149" t="s">
         <v>48</v>
@@ -11855,7 +11840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -11884,7 +11869,7 @@
         <v>24</v>
       </c>
       <c r="J150" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K150" t="s">
         <v>50</v>
@@ -11893,7 +11878,7 @@
         <v>51</v>
       </c>
       <c r="M150" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="N150" t="s">
         <v>32</v>
@@ -11908,7 +11893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -11937,7 +11922,7 @@
         <v>24</v>
       </c>
       <c r="J151" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K151" t="s">
         <v>48</v>

--- a/data/raw/GLNPO 2024 Spring/Huron/D20/Zoops/HU 61 D20 QA Spring 2024 24GH02Q74 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Huron/D20/Zoops/HU 61 D20 QA Spring 2024 24GH02Q74 Zoop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Huron\D20\Zoops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F3385D-0054-4D7C-B68E-F5D23935E86B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC826046-3BED-4ACA-869C-3CEC66208DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6D1FDE3E-6719-49BA-9F61-2AC28C8DE547}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="20" r:id="rId2"/>
+    <pivotCache cacheId="29" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3281,7 +3281,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B136E1C2-44DE-459E-8694-7E4BB02EA264}" name="PivotTable3" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B136E1C2-44DE-459E-8694-7E4BB02EA264}" name="PivotTable3" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T3:X15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -11828,7 +11828,7 @@
         <v>32</v>
       </c>
       <c r="N149" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O149" t="s">
         <v>29</v>
@@ -11881,7 +11881,7 @@
         <v>27</v>
       </c>
       <c r="N150" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="O150" t="s">
         <v>29</v>
@@ -11934,7 +11934,7 @@
         <v>32</v>
       </c>
       <c r="N151" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O151" t="s">
         <v>29</v>

--- a/data/raw/GLNPO 2024 Spring/Huron/D20/Zoops/HU 61 D20 QA Spring 2024 24GH02Q74 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Huron/D20/Zoops/HU 61 D20 QA Spring 2024 24GH02Q74 Zoop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Huron\D20\Zoops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC826046-3BED-4ACA-869C-3CEC66208DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FFC391-3DCC-4A30-BE46-2A2649F3D919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6D1FDE3E-6719-49BA-9F61-2AC28C8DE547}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="29" r:id="rId2"/>
+    <pivotCache cacheId="8" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3281,7 +3281,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B136E1C2-44DE-459E-8694-7E4BB02EA264}" name="PivotTable3" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B136E1C2-44DE-459E-8694-7E4BB02EA264}" name="PivotTable3" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T3:X15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -3711,9 +3711,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5124763D-8627-4458-AC86-27EBBD8020BE}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:X151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
@@ -3785,7 +3787,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3838,7 +3840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3897,7 +3899,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -3965,7 +3967,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4030,7 +4032,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -4095,7 +4097,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -4160,7 +4162,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -4222,7 +4224,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -4284,7 +4286,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -4346,7 +4348,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -4414,7 +4416,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -4482,7 +4484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -4547,7 +4549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -4612,7 +4614,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -4680,7 +4682,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -4733,7 +4735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -4786,7 +4788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -4839,7 +4841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -4897,7 +4899,7 @@
       <c r="U19" s="5"/>
       <c r="V19" s="5"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -4959,7 +4961,7 @@
         <v>1.004</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -5019,7 +5021,7 @@
         <v>1.002</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -5081,7 +5083,7 @@
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -5141,7 +5143,7 @@
         <v>0.998</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -5201,7 +5203,7 @@
       </c>
       <c r="V24" s="5"/>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -5261,7 +5263,7 @@
       </c>
       <c r="V25" s="5"/>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -5321,7 +5323,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -5374,7 +5376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -5427,7 +5429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -5480,7 +5482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -5533,7 +5535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -5586,7 +5588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -5639,7 +5641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -5692,7 +5694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -5745,7 +5747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -5798,7 +5800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -5851,7 +5853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -5904,7 +5906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -5957,7 +5959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -6010,7 +6012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -6063,7 +6065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -6116,7 +6118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -6169,7 +6171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -6263,7 +6265,7 @@
         <v>32</v>
       </c>
       <c r="N44" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O44">
         <v>2.8050000000000002</v>
@@ -6328,7 +6330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -6381,7 +6383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -6434,7 +6436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -6487,7 +6489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -6540,7 +6542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -6593,7 +6595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -6646,7 +6648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -6699,7 +6701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -6752,7 +6754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -6805,7 +6807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -6858,7 +6860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -6911,7 +6913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -6964,7 +6966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -7017,7 +7019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -7070,7 +7072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -7123,7 +7125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -7176,7 +7178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -7229,7 +7231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -7282,7 +7284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -7335,7 +7337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -7388,7 +7390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -7441,7 +7443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -7494,7 +7496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -7547,7 +7549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -7600,7 +7602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -7653,7 +7655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -7706,7 +7708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -7759,7 +7761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -7812,7 +7814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -7865,7 +7867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -7918,7 +7920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -7971,7 +7973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -8024,7 +8026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -8077,7 +8079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -8130,7 +8132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -8183,7 +8185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -8236,7 +8238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -8289,7 +8291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -8342,7 +8344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -8395,7 +8397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -8448,7 +8450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -8501,7 +8503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -8554,7 +8556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -8607,7 +8609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -8660,7 +8662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -8713,7 +8715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -8766,7 +8768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -8819,7 +8821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -8872,7 +8874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -8925,7 +8927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -8978,7 +8980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -9031,7 +9033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -9084,7 +9086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -9137,7 +9139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -9190,7 +9192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -9243,7 +9245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -9296,7 +9298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -9349,7 +9351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -9402,7 +9404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -9455,7 +9457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -9508,7 +9510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -9561,7 +9563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -9614,7 +9616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -9667,7 +9669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -9720,7 +9722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -9773,7 +9775,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -9826,7 +9828,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -9879,7 +9881,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -9932,7 +9934,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -9985,7 +9987,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -10038,7 +10040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -10091,7 +10093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -10144,7 +10146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -10197,7 +10199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -10250,7 +10252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -10303,7 +10305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -10356,7 +10358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -10409,7 +10411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -10462,7 +10464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -10515,7 +10517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -10568,7 +10570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -10621,7 +10623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -10674,7 +10676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -10727,7 +10729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -10780,7 +10782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -10833,7 +10835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -10886,7 +10888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -10939,7 +10941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -10992,7 +10994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -11045,7 +11047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -11098,7 +11100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -11151,7 +11153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -11204,7 +11206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -11257,7 +11259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -11310,7 +11312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -11363,7 +11365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -11416,7 +11418,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -11469,7 +11471,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -11522,7 +11524,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -11575,7 +11577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -11628,7 +11630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -11681,7 +11683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -11734,7 +11736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -11947,6 +11949,14 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R151" xr:uid="{5124763D-8627-4458-AC86-27EBBD8020BE}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Senecella calanoides"/>
+        <filter val="Senecella copepodites"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>